--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.91601848381733</v>
+        <v>6.973853003620316</v>
       </c>
       <c r="D2" t="n">
-        <v>28.63564212655271</v>
+        <v>4.653291845564815</v>
       </c>
       <c r="E2" t="n">
-        <v>19.23546638228721</v>
+        <v>3.125763287121671</v>
       </c>
       <c r="F2" t="n">
-        <v>19.23916679580827</v>
+        <v>3.126364604318844</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.79326485209516</v>
+        <v>1.753905538465464</v>
       </c>
       <c r="D3" t="n">
-        <v>7.969340036843536</v>
+        <v>1.295017755987075</v>
       </c>
       <c r="E3" t="n">
-        <v>19.23546638228721</v>
+        <v>3.125763287121671</v>
       </c>
       <c r="F3" t="n">
-        <v>19.23916679580827</v>
+        <v>3.126364604318844</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.70801283541185</v>
+        <v>4.665052085754425</v>
       </c>
       <c r="D4" t="n">
-        <v>27.29538677801212</v>
+        <v>4.43550035142697</v>
       </c>
       <c r="E4" t="n">
-        <v>19.23546638228721</v>
+        <v>3.125763287121671</v>
       </c>
       <c r="F4" t="n">
-        <v>19.23916679580827</v>
+        <v>3.126364604318844</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.60372621744882</v>
+        <v>8.223105510335433</v>
       </c>
       <c r="D5" t="n">
-        <v>43.61964098486514</v>
+        <v>7.088191660040585</v>
       </c>
       <c r="E5" t="n">
-        <v>19.23546638228721</v>
+        <v>3.125763287121671</v>
       </c>
       <c r="F5" t="n">
-        <v>19.23916679580827</v>
+        <v>3.126364604318844</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.18670935643931</v>
+        <v>2.467840270421389</v>
       </c>
       <c r="D6" t="n">
-        <v>15.56591068642236</v>
+        <v>2.529460486543634</v>
       </c>
       <c r="E6" t="n">
-        <v>19.23546638228721</v>
+        <v>3.125763287121671</v>
       </c>
       <c r="F6" t="n">
-        <v>19.23916679580827</v>
+        <v>3.126364604318844</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>57.81384605106636</v>
+        <v>9.394749983298285</v>
       </c>
       <c r="D7" t="n">
-        <v>58.31091889386345</v>
+        <v>9.475524320252811</v>
       </c>
       <c r="E7" t="n">
-        <v>19.23546638228721</v>
+        <v>3.125763287121671</v>
       </c>
       <c r="F7" t="n">
-        <v>19.23916679580827</v>
+        <v>3.126364604318844</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>63.87642676917541</v>
+        <v>10.379919349991</v>
       </c>
       <c r="D8" t="n">
-        <v>62.66299646979638</v>
+        <v>10.18273692634191</v>
       </c>
       <c r="E8" t="n">
-        <v>19.23546638228721</v>
+        <v>3.125763287121671</v>
       </c>
       <c r="F8" t="n">
-        <v>19.23916679580827</v>
+        <v>3.126364604318844</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
